--- a/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.224616765975952</v>
+        <v>1.190037488937378</v>
       </c>
       <c r="E2" t="n">
         <v>0.9893529482385016</v>
@@ -503,7 +503,7 @@
         <v>0.9824284292349985</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9996907854050711</v>
+        <v>0.9996907854050712</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.056440830230713</v>
+        <v>1.896123170852661</v>
       </c>
       <c r="E3" t="n">
         <v>0.9914820069145582</v>
@@ -538,7 +538,7 @@
         <v>0.9824284292349985</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9996907854050711</v>
+        <v>0.9996907854050712</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.224616765975952</v>
+        <v>1.190037488937378</v>
       </c>
       <c r="E2" t="n">
         <v>0.9893529482385016</v>
@@ -634,7 +634,7 @@
         <v>0.9824284292349985</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9996907854050711</v>
+        <v>0.9996907854050712</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.056440830230713</v>
+        <v>1.896123170852661</v>
       </c>
       <c r="E3" t="n">
         <v>0.9914820069145582</v>
@@ -669,7 +669,7 @@
         <v>0.9824284292349985</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9996907854050711</v>
+        <v>0.9996907854050712</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.190037488937378</v>
+        <v>0.9002141952514648</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9893529482385016</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F2" t="n">
-        <v>0.987012987012987</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9824284292349985</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9996907854050712</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'max_features': 0.6, 'max_samples': 0.8, 'n_estimators': 100}</t>
+          <t>{'max_features': 0.6, 'max_samples': 0.6, 'n_estimators': 25}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.896123170852661</v>
+        <v>1.457194566726685</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9914820069145582</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F3" t="n">
-        <v>0.987012987012987</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9824284292349985</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9996907854050712</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_features': 0.6, 'max_samples': 0.8, 'n_estimators': 100}</t>
+          <t>{'max_features': 0.6, 'max_samples': 0.6, 'n_estimators': 25}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.190037488937378</v>
+        <v>0.9002141952514648</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9893529482385016</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F2" t="n">
-        <v>0.987012987012987</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9824284292349985</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9996907854050712</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'max_features': 0.6, 'max_samples': 0.8, 'n_estimators': 100}</t>
+          <t>{'max_features': 0.6, 'max_samples': 0.6, 'n_estimators': 25}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.896123170852661</v>
+        <v>1.457194566726685</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9914820069145582</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F3" t="n">
-        <v>0.987012987012987</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9824284292349985</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9996907854050712</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_features': 0.6, 'max_samples': 0.8, 'n_estimators': 100}</t>
+          <t>{'max_features': 0.6, 'max_samples': 0.6, 'n_estimators': 25}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9002141952514648</v>
+        <v>1.150292873382568</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9983593504958139</v>
+        <v>0.8247979524211558</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8435374149659864</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.8172089314194576</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0.96343537414966</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'max_features': 0.6, 'max_samples': 0.6, 'n_estimators': 25}</t>
+          <t>{'max_features': 0.8, 'max_samples': 0.8, 'n_estimators': 50}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.457194566726685</v>
+        <v>1.832776308059692</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.8302894670939711</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8367346938775511</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.7963664405769668</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.9614801702994122</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_features': 0.6, 'max_samples': 0.6, 'n_estimators': 25}</t>
+          <t>{'max_features': 0.8, 'max_samples': 0.8, 'n_estimators': 100}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3.789657831192017</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.8317587282146768</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8116392379550273</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9630767272895553</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'max_features': 0.8, 'max_samples': 1.0, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9002141952514648</v>
+        <v>1.150292873382568</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9983593504958139</v>
+        <v>0.8247979524211558</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8435374149659864</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.8172089314194576</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0.96343537414966</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'max_features': 0.6, 'max_samples': 0.6, 'n_estimators': 25}</t>
+          <t>{'max_features': 0.8, 'max_samples': 0.8, 'n_estimators': 50}</t>
         </is>
       </c>
     </row>
@@ -657,23 +692,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.457194566726685</v>
+        <v>1.832776308059692</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.8302894670939711</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8367346938775511</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.7963664405769668</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.9614801702994122</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_features': 0.6, 'max_samples': 0.6, 'n_estimators': 25}</t>
+          <t>{'max_features': 0.8, 'max_samples': 0.8, 'n_estimators': 100}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3.789657831192017</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.8317587282146768</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8116392379550273</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9630767272895553</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'max_features': 0.8, 'max_samples': 1.0, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.150292873382568</v>
+        <v>15747.45786547661</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8247979524211558</v>
+        <v>0.9280699341723085</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8435374149659864</v>
+        <v>0.950517836593786</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8172089314194576</v>
+        <v>0.932054070173397</v>
       </c>
       <c r="H2" t="n">
-        <v>0.96343537414966</v>
+        <v>0.9845430034684587</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'max_features': 0.8, 'max_samples': 0.8, 'n_estimators': 50}</t>
+          <t>{'max_features': 1.0, 'max_samples': 0.8, 'n_estimators': 50}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.832776308059692</v>
+        <v>18.41933584213257</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8302894670939711</v>
+        <v>0.928876610929035</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8367346938775511</v>
+        <v>0.9485040276179517</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7963664405769668</v>
+        <v>0.9296640638468039</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9614801702994122</v>
+        <v>0.9831533618758581</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_features': 0.8, 'max_samples': 0.8, 'n_estimators': 100}</t>
+          <t>{'max_features': 1.0, 'max_samples': 0.6, 'n_estimators': 25}</t>
         </is>
       </c>
     </row>
@@ -561,23 +561,23 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>3.789657831192017</v>
+        <v>32.46850252151489</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8317587282146768</v>
+        <v>0.9322375683739018</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.9508055235903338</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8116392379550273</v>
+        <v>0.9329165872415834</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9630767272895553</v>
+        <v>0.9847139424813932</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'max_features': 0.8, 'max_samples': 1.0, 'n_estimators': 100}</t>
+          <t>{'max_features': 1.0, 'max_samples': 0.6, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.150292873382568</v>
+        <v>15747.45786547661</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8247979524211558</v>
+        <v>0.9280699341723085</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8435374149659864</v>
+        <v>0.950517836593786</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8172089314194576</v>
+        <v>0.932054070173397</v>
       </c>
       <c r="H2" t="n">
-        <v>0.96343537414966</v>
+        <v>0.9845430034684587</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'max_features': 0.8, 'max_samples': 0.8, 'n_estimators': 50}</t>
+          <t>{'max_features': 1.0, 'max_samples': 0.8, 'n_estimators': 50}</t>
         </is>
       </c>
     </row>
@@ -692,23 +692,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.832776308059692</v>
+        <v>18.41933584213257</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8302894670939711</v>
+        <v>0.928876610929035</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8367346938775511</v>
+        <v>0.9485040276179517</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7963664405769668</v>
+        <v>0.9296640638468039</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9614801702994122</v>
+        <v>0.9831533618758581</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_features': 0.8, 'max_samples': 0.8, 'n_estimators': 100}</t>
+          <t>{'max_features': 1.0, 'max_samples': 0.6, 'n_estimators': 25}</t>
         </is>
       </c>
     </row>
@@ -727,23 +727,23 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>3.789657831192017</v>
+        <v>32.46850252151489</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8317587282146768</v>
+        <v>0.9322375683739018</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.9508055235903338</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8116392379550273</v>
+        <v>0.9329165872415834</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9630767272895553</v>
+        <v>0.9847139424813932</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'max_features': 0.8, 'max_samples': 1.0, 'n_estimators': 100}</t>
+          <t>{'max_features': 1.0, 'max_samples': 0.6, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>15747.45786547661</v>
+        <v>1.167033195495605</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9280699341723085</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F2" t="n">
-        <v>0.950517836593786</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.932054070173397</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9845430034684587</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'max_features': 1.0, 'max_samples': 0.8, 'n_estimators': 50}</t>
+          <t>{'max_features': 0.6, 'max_samples': 0.6, 'n_estimators': 25}</t>
         </is>
       </c>
     </row>
@@ -526,58 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>18.41933584213257</v>
+        <v>1.731572151184082</v>
       </c>
       <c r="E3" t="n">
-        <v>0.928876610929035</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9485040276179517</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9296640638468039</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9831533618758581</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_features': 1.0, 'max_samples': 0.6, 'n_estimators': 25}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Bagging</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>32.46850252151489</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9322375683739018</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9508055235903338</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.9329165872415834</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.9847139424813932</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'max_features': 1.0, 'max_samples': 0.6, 'n_estimators': 100}</t>
+          <t>{'max_features': 0.6, 'max_samples': 0.6, 'n_estimators': 25}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>15747.45786547661</v>
+        <v>1.167033195495605</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9280699341723085</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F2" t="n">
-        <v>0.950517836593786</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.932054070173397</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9845430034684587</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'max_features': 1.0, 'max_samples': 0.8, 'n_estimators': 50}</t>
+          <t>{'max_features': 0.6, 'max_samples': 0.6, 'n_estimators': 25}</t>
         </is>
       </c>
     </row>
@@ -692,58 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>18.41933584213257</v>
+        <v>1.731572151184082</v>
       </c>
       <c r="E3" t="n">
-        <v>0.928876610929035</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9485040276179517</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9296640638468039</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9831533618758581</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_features': 1.0, 'max_samples': 0.6, 'n_estimators': 25}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Bagging</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>32.46850252151489</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9322375683739018</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9508055235903338</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.9329165872415834</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.9847139424813932</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'max_features': 1.0, 'max_samples': 0.6, 'n_estimators': 100}</t>
+          <t>{'max_features': 0.6, 'max_samples': 0.6, 'n_estimators': 25}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.167033195495605</v>
+        <v>1.193494558334351</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.731572151184082</v>
+        <v>1.790854692459106</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.167033195495605</v>
+        <v>1.193494558334351</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.731572151184082</v>
+        <v>1.790854692459106</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>

--- a/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.193494558334351</v>
+        <v>1.203188419342041</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.790854692459106</v>
+        <v>1.769453525543213</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.193494558334351</v>
+        <v>1.203188419342041</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.790854692459106</v>
+        <v>1.769453525543213</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>

--- a/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.203188419342041</v>
+        <v>0.7404987812042236</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -507,7 +507,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'max_features': 0.6, 'max_samples': 0.6, 'n_estimators': 25}</t>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.769453525543213</v>
+        <v>1.154060363769531</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -542,7 +542,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_features': 0.6, 'max_samples': 0.6, 'n_estimators': 25}</t>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.203188419342041</v>
+        <v>0.7404987812042236</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -638,7 +638,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'max_features': 0.6, 'max_samples': 0.6, 'n_estimators': 25}</t>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.769453525543213</v>
+        <v>1.154060363769531</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -673,7 +673,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_features': 0.6, 'max_samples': 0.6, 'n_estimators': 25}</t>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7404987812042236</v>
+        <v>6.78164267539978</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9983593504958139</v>
+        <v>0.9280699341723085</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.950517836593786</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.932054070173397</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0.9845430034684587</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.154060363769531</v>
+        <v>12.55758929252625</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.928876610929035</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9485040276179517</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9296640638468039</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.9831533618758581</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'n_estimators': 25, 'max_samples': 0.6, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7404987812042236</v>
+        <v>6.78164267539978</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9983593504958139</v>
+        <v>0.9280699341723085</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.950517836593786</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.932054070173397</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0.9845430034684587</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.154060363769531</v>
+        <v>12.55758929252625</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.928876610929035</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9485040276179517</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9296640638468039</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.9831533618758581</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'n_estimators': 25, 'max_samples': 0.6, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>6.78164267539978</v>
+        <v>8.419467449188232</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9280699341723085</v>
+        <v>0.4014059208840891</v>
       </c>
       <c r="F2" t="n">
-        <v>0.950517836593786</v>
+        <v>0.6625</v>
       </c>
       <c r="G2" t="n">
-        <v>0.932054070173397</v>
+        <v>0.3255960824427653</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9845430034684587</v>
+        <v>0.9295488281250001</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 50, 'max_samples': 1.0, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>
@@ -523,26 +523,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>12.55758929252625</v>
+        <v>10.71219110488892</v>
       </c>
       <c r="E3" t="n">
-        <v>0.928876610929035</v>
+        <v>0.4264174942342238</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9485040276179517</v>
+        <v>0.659375</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9296640638468039</v>
+        <v>0.3267092546117172</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9831533618758581</v>
+        <v>0.9313486328124999</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 25, 'max_samples': 0.6, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 25, 'max_samples': 1.0, 'max_features': 0.8}</t>
         </is>
       </c>
     </row>
@@ -619,26 +619,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>6.78164267539978</v>
+        <v>8.419467449188232</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9280699341723085</v>
+        <v>0.4014059208840891</v>
       </c>
       <c r="F2" t="n">
-        <v>0.950517836593786</v>
+        <v>0.6625</v>
       </c>
       <c r="G2" t="n">
-        <v>0.932054070173397</v>
+        <v>0.3255960824427653</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9845430034684587</v>
+        <v>0.9295488281250001</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 50, 'max_samples': 1.0, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>
@@ -654,26 +654,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>12.55758929252625</v>
+        <v>10.71219110488892</v>
       </c>
       <c r="E3" t="n">
-        <v>0.928876610929035</v>
+        <v>0.4264174942342238</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9485040276179517</v>
+        <v>0.659375</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9296640638468039</v>
+        <v>0.3267092546117172</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9831533618758581</v>
+        <v>0.9313486328124999</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 25, 'max_samples': 0.6, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 25, 'max_samples': 1.0, 'max_features': 0.8}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>8.419467449188232</v>
+        <v>29.3004412651062</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4014059208840891</v>
+        <v>0.7521014360203813</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6625</v>
+        <v>0.9450215353432987</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3255960824427653</v>
+        <v>0.7897204739826351</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9295488281250001</v>
+        <v>0.9349533341276461</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'max_samples': 1.0, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
         </is>
       </c>
     </row>
@@ -523,26 +523,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>10.71219110488892</v>
+        <v>57.42630863189697</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4264174942342238</v>
+        <v>0.7677588908801928</v>
       </c>
       <c r="F3" t="n">
-        <v>0.659375</v>
+        <v>0.9445148213833291</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3267092546117172</v>
+        <v>0.7926083122896885</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9313486328124999</v>
+        <v>0.9250530203741212</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 25, 'max_samples': 1.0, 'max_features': 0.8}</t>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.8}</t>
         </is>
       </c>
     </row>
@@ -619,26 +619,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>8.419467449188232</v>
+        <v>29.3004412651062</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4014059208840891</v>
+        <v>0.7521014360203813</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6625</v>
+        <v>0.9450215353432987</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3255960824427653</v>
+        <v>0.7897204739826351</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9295488281250001</v>
+        <v>0.9349533341276461</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'max_samples': 1.0, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
         </is>
       </c>
     </row>
@@ -654,26 +654,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>10.71219110488892</v>
+        <v>57.42630863189697</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4264174942342238</v>
+        <v>0.7677588908801928</v>
       </c>
       <c r="F3" t="n">
-        <v>0.659375</v>
+        <v>0.9445148213833291</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3267092546117172</v>
+        <v>0.7926083122896885</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9313486328124999</v>
+        <v>0.9250530203741212</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 25, 'max_samples': 1.0, 'max_features': 0.8}</t>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.8}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>29.3004412651062</v>
+        <v>0.7135782241821289</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7521014360203813</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9450215353432987</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7897204739826351</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9349533341276461</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>57.42630863189697</v>
+        <v>1.323484182357788</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7677588908801928</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9445148213833291</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7926083122896885</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9250530203741212</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.8}</t>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
         </is>
       </c>
     </row>
@@ -622,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>29.3004412651062</v>
+        <v>0.7135782241821289</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7521014360203813</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9450215353432987</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7897204739826351</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9349533341276461</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>57.42630863189697</v>
+        <v>1.323484182357788</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7677588908801928</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9445148213833291</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7926083122896885</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9250530203741212</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.8}</t>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7135782241821289</v>
+        <v>0.649118185043335</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.323484182357788</v>
+        <v>1.075996160507202</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7135782241821289</v>
+        <v>0.649118185043335</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.323484182357788</v>
+        <v>1.075996160507202</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>

--- a/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.649118185043335</v>
+        <v>0.6855957508087158</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.075996160507202</v>
+        <v>1.136143445968628</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.649118185043335</v>
+        <v>0.6855957508087158</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.075996160507202</v>
+        <v>1.136143445968628</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>

--- a/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6855957508087158</v>
+        <v>1.096622705459595</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.136143445968628</v>
+        <v>1.609349012374878</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -541,6 +541,41 @@
         <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.971560955047607</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9983535762483131</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
         </is>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,7 +657,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6855957508087158</v>
+        <v>1.096622705459595</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -657,7 +692,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.136143445968628</v>
+        <v>1.609349012374878</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -672,6 +707,41 @@
         <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.971560955047607</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9983535762483131</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
         </is>

--- a/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.096622705459595</v>
+        <v>0.8900933265686035</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.609349012374878</v>
+        <v>1.469369411468506</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -561,7 +561,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>2.971560955047607</v>
+        <v>2.90601921081543</v>
       </c>
       <c r="E4" t="n">
         <v>0.9983535762483131</v>
@@ -657,7 +657,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.096622705459595</v>
+        <v>0.8900933265686035</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -692,7 +692,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.609349012374878</v>
+        <v>1.469369411468506</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -727,7 +727,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>2.971560955047607</v>
+        <v>2.90601921081543</v>
       </c>
       <c r="E4" t="n">
         <v>0.9983535762483131</v>

--- a/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8900933265686035</v>
+        <v>4.598600149154663</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9983593504958139</v>
+        <v>0.9280699341723085</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.950517836593786</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.932054070173397</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0.9845430034684587</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>
@@ -526,58 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.469369411468506</v>
+        <v>8.56904125213623</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.928876610929035</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9485040276179517</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9296640638468039</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.9831533618758581</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Bagging</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2.90601921081543</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9983535762483131</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9935064935064936</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.9934996412139632</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'n_estimators': 25, 'max_samples': 0.6, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8900933265686035</v>
+        <v>4.598600149154663</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9983593504958139</v>
+        <v>0.9280699341723085</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.950517836593786</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.932054070173397</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0.9845430034684587</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>
@@ -692,58 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.469369411468506</v>
+        <v>8.56904125213623</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.928876610929035</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9485040276179517</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9296640638468039</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.9831533618758581</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Bagging</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2.90601921081543</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9983535762483131</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9935064935064936</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.9934996412139632</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'n_estimators': 25, 'max_samples': 0.6, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>4.598600149154663</v>
+        <v>14.81787252426147</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9280699341723085</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.950517836593786</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.932054070173397</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9845430034684587</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>8.56904125213623</v>
+        <v>27.44591641426086</v>
       </c>
       <c r="E3" t="n">
-        <v>0.928876610929035</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9485040276179517</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9296640638468039</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9831533618758581</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 25, 'max_samples': 0.6, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>4.598600149154663</v>
+        <v>14.81787252426147</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9280699341723085</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.950517836593786</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.932054070173397</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9845430034684587</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>8.56904125213623</v>
+        <v>27.44591641426086</v>
       </c>
       <c r="E3" t="n">
-        <v>0.928876610929035</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9485040276179517</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9296640638468039</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9831533618758581</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 25, 'max_samples': 0.6, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>14.81787252426147</v>
+        <v>14.96656465530396</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>27.44591641426086</v>
+        <v>38.96033000946045</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>14.81787252426147</v>
+        <v>14.96656465530396</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>27.44591641426086</v>
+        <v>38.96033000946045</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>

--- a/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>14.96656465530396</v>
+        <v>30.05495476722717</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0.7521014360203813</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.9450215353432987</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0.7897204739826351</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0.9349533341276461</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>38.96033000946045</v>
+        <v>58.17849445343018</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0.7677588908801928</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0.9445148213833291</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0.7926083122896885</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.9250530203741212</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.8}</t>
         </is>
       </c>
     </row>
@@ -622,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>14.96656465530396</v>
+        <v>30.05495476722717</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0.7521014360203813</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.9450215353432987</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0.7897204739826351</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0.9349533341276461</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>38.96033000946045</v>
+        <v>58.17849445343018</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0.7677588908801928</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0.9445148213833291</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0.7926083122896885</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.9250530203741212</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.8}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>30.05495476722717</v>
+        <v>74.81637406349182</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7521014360203813</v>
+        <v>0.9421905253471752</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9450215353432987</v>
+        <v>0.9555607806254409</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7897204739826351</v>
+        <v>0.9476193061066791</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9349533341276461</v>
+        <v>0.9891931774364535</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 0.6}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>58.17849445343018</v>
+        <v>153.9736731052399</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7677588908801928</v>
+        <v>0.9459086431217779</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9445148213833291</v>
+        <v>0.9562661650599577</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7926083122896885</v>
+        <v>0.9485504116966064</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9250530203741212</v>
+        <v>0.9887731762387013</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.8}</t>
+          <t>{'n_estimators': 100, 'max_samples': 0.6, 'max_features': 0.8}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>30.05495476722717</v>
+        <v>74.81637406349182</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7521014360203813</v>
+        <v>0.9421905253471752</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9450215353432987</v>
+        <v>0.9555607806254409</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7897204739826351</v>
+        <v>0.9476193061066791</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9349533341276461</v>
+        <v>0.9891931774364535</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 0.6}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>58.17849445343018</v>
+        <v>153.9736731052399</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7677588908801928</v>
+        <v>0.9459086431217779</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9445148213833291</v>
+        <v>0.9562661650599577</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7926083122896885</v>
+        <v>0.9485504116966064</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9250530203741212</v>
+        <v>0.9887731762387013</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.8}</t>
+          <t>{'n_estimators': 100, 'max_samples': 0.6, 'max_features': 0.8}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>74.81637406349182</v>
+        <v>3.838783740997314</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9421905253471752</v>
+        <v>0.3702938726305914</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9555607806254409</v>
+        <v>0.6795918367346939</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9476193061066791</v>
+        <v>0.4957490656219858</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9891931774364535</v>
+        <v>0.9393980806608357</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 0.6}</t>
+          <t>{'max_features': 1.0, 'max_samples': 1.0, 'n_estimators': 25}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>153.9736731052399</v>
+        <v>7.496529817581177</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9459086431217779</v>
+        <v>0.3947567302277579</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9562661650599577</v>
+        <v>0.6938775510204082</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9485504116966064</v>
+        <v>0.5166914607998288</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9887731762387013</v>
+        <v>0.9459208836595863</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 0.6, 'max_features': 0.8}</t>
+          <t>{'max_features': 1.0, 'max_samples': 0.8, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>74.81637406349182</v>
+        <v>3.838783740997314</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9421905253471752</v>
+        <v>0.3702938726305914</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9555607806254409</v>
+        <v>0.6795918367346939</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9476193061066791</v>
+        <v>0.4957490656219858</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9891931774364535</v>
+        <v>0.9393980806608357</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 0.6}</t>
+          <t>{'max_features': 1.0, 'max_samples': 1.0, 'n_estimators': 25}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>153.9736731052399</v>
+        <v>7.496529817581177</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9459086431217779</v>
+        <v>0.3947567302277579</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9562661650599577</v>
+        <v>0.6938775510204082</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9485504116966064</v>
+        <v>0.5166914607998288</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9887731762387013</v>
+        <v>0.9459208836595863</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 0.6, 'max_features': 0.8}</t>
+          <t>{'max_features': 1.0, 'max_samples': 0.8, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.838783740997314</v>
+        <v>0.8552136421203613</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3702938726305914</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6795918367346939</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4957490656219858</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9393980806608357</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'max_features': 1.0, 'max_samples': 1.0, 'n_estimators': 25}</t>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>7.496529817581177</v>
+        <v>1.467958688735962</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3947567302277579</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6938775510204082</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5166914607998288</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9459208836595863</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_features': 1.0, 'max_samples': 0.8, 'n_estimators': 100}</t>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.607017993927002</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9983535762483131</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.838783740997314</v>
+        <v>0.8552136421203613</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3702938726305914</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6795918367346939</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4957490656219858</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9393980806608357</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'max_features': 1.0, 'max_samples': 1.0, 'n_estimators': 25}</t>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
         </is>
       </c>
     </row>
@@ -657,23 +692,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>7.496529817581177</v>
+        <v>1.467958688735962</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3947567302277579</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6938775510204082</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5166914607998288</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9459208836595863</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_features': 1.0, 'max_samples': 0.8, 'n_estimators': 100}</t>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.607017993927002</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9983535762483131</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8552136421203613</v>
+        <v>1.168156385421753</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.467958688735962</v>
+        <v>2.015239477157593</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -561,7 +561,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>2.607017993927002</v>
+        <v>3.985295057296753</v>
       </c>
       <c r="E4" t="n">
         <v>0.9983535762483131</v>
@@ -657,7 +657,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8552136421203613</v>
+        <v>1.168156385421753</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -692,7 +692,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.467958688735962</v>
+        <v>2.015239477157593</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -727,7 +727,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>2.607017993927002</v>
+        <v>3.985295057296753</v>
       </c>
       <c r="E4" t="n">
         <v>0.9983535762483131</v>

--- a/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>1.168156385421753</v>
+        <v>22.2285475730896</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9983593504958139</v>
+        <v>0.9122105898905353</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9280405405405405</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9210462943865704</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0.9785067669714204</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>
@@ -523,61 +523,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>2.015239477157593</v>
+        <v>47.55513858795166</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.9125947712270616</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.925</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9176556212519473</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.9791446700101585</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Bagging</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>3.985295057296753</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9983535762483131</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9935064935064936</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.9934996412139632</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -654,26 +619,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>1.168156385421753</v>
+        <v>22.2285475730896</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9983593504958139</v>
+        <v>0.9122105898905353</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9280405405405405</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9210462943865704</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0.9785067669714204</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>
@@ -689,61 +654,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>2.015239477157593</v>
+        <v>47.55513858795166</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.9125947712270616</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.925</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9176556212519473</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.9791446700101585</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Bagging</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>3.985295057296753</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9983535762483131</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9935064935064936</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.9934996412139632</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>22.2285475730896</v>
+        <v>13.85714769363403</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9122105898905353</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9280405405405405</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9210462943865704</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9785067669714204</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 0.8}</t>
         </is>
       </c>
     </row>
@@ -523,26 +523,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>47.55513858795166</v>
+        <v>25.87836480140686</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9125947712270616</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.925</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9176556212519473</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9791446700101585</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 0.8}</t>
         </is>
       </c>
     </row>
@@ -619,26 +619,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>22.2285475730896</v>
+        <v>13.85714769363403</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9122105898905353</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9280405405405405</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9210462943865704</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9785067669714204</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 0.8}</t>
         </is>
       </c>
     </row>
@@ -654,26 +654,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>47.55513858795166</v>
+        <v>25.87836480140686</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9125947712270616</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.925</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9176556212519473</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9791446700101585</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 0.8}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>13.85714769363403</v>
+        <v>11.07282543182373</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>25.87836480140686</v>
+        <v>21.25451612472534</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>13.85714769363403</v>
+        <v>11.07282543182373</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>25.87836480140686</v>
+        <v>21.25451612472534</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
